--- a/data/trans_orig/Q24D_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Clase-trans_orig.xlsx
@@ -526,7 +526,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Número medio de veces que han intentado dejar de fumar</t>
+          <t>Número medio de veces que han intentado dejar de fumar (tasa de respuesta: 91,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -721,57 +721,57 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,32; 3,56</t>
+          <t>2,3; 3,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 4,22</t>
+          <t>2,02; 4,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,07</t>
+          <t>2,23; 3,88</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,74; 3,32</t>
+          <t>1,73; 3,45</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,7; 3,87</t>
+          <t>2,69; 3,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,7; 2,44</t>
+          <t>1,71; 2,43</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,06; 3,17</t>
+          <t>2,11; 3,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,64</t>
+          <t>1,89; 2,66</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,44</t>
+          <t>2,56; 3,43</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,41</t>
+          <t>2,03; 3,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,31</t>
+          <t>2,28; 3,27</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,58</t>
+          <t>2,26; 4,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,34; 3,22</t>
+          <t>2,36; 3,2</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,82</t>
+          <t>1,75; 2,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 4,22</t>
+          <t>2,25; 4,39</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,4</t>
+          <t>1,69; 2,39</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,57</t>
+          <t>1,87; 2,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,66; 2,39</t>
+          <t>1,67; 2,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,98; 2,79</t>
+          <t>1,97; 2,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,1; 3,37</t>
+          <t>2,08; 3,29</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,76</t>
+          <t>2,22; 2,82</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,47</t>
+          <t>1,8; 2,48</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,34</t>
+          <t>2,23; 3,39</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,49</t>
+          <t>2,28; 4,33</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 3,24</t>
+          <t>2,26; 3,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>2,24; 3,09</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2,08; 3,96</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1,35; 2,07</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,94; 2,68</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1,96; 3,97</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2,34; 4,82</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2,23; 4,05</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>2,24; 2,97</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
           <t>2,27; 3,05</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2,09; 4,04</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1,35; 2,09</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,88; 2,69</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>1,92; 4,17</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2,29; 4,7</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>2,22; 3,83</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>2,26; 3,06</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2,3; 3,12</t>
-        </is>
-      </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 4,06</t>
+          <t>2,26; 3,97</t>
         </is>
       </c>
     </row>
@@ -1136,42 +1136,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,43; 3,66</t>
+          <t>2,39; 3,62</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,58</t>
+          <t>2,44; 3,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,45; 3,19</t>
+          <t>2,42; 3,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,94</t>
+          <t>2,28; 4,98</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,78; 2,39</t>
+          <t>1,81; 2,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>2,16; 2,97</t>
+          <t>2,18; 3,07</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,32; 2,99</t>
+          <t>2,28; 2,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,6; 3,73</t>
+          <t>2,65; 3,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,47; 2,93</t>
+          <t>2,44; 2,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,57; 4,05</t>
+          <t>2,58; 4,05</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1276,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,13; 5,29</t>
+          <t>2,1; 5,23</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,06; 2,9</t>
+          <t>2,05; 2,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,09; 2,87</t>
+          <t>2,1; 2,89</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,62; 4,69</t>
+          <t>2,65; 4,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,86; 2,59</t>
+          <t>1,88; 2,59</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,89</t>
+          <t>2,21; 2,87</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,93</t>
+          <t>2,18; 2,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,88</t>
+          <t>2,18; 3,76</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,12; 3,82</t>
+          <t>2,14; 3,87</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 2,78</t>
+          <t>2,26; 2,77</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,77</t>
+          <t>2,24; 2,82</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,78</t>
+          <t>2,51; 3,72</t>
         </is>
       </c>
     </row>
@@ -1416,17 +1416,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,93</t>
+          <t>1,16; 2,96</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,91; 4,25</t>
+          <t>1,89; 4,17</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,65; 3,09</t>
+          <t>1,67; 3,15</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 3,26</t>
+          <t>2,28; 3,45</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,85</t>
+          <t>1,8; 2,79</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,1; 4,8</t>
+          <t>2,07; 4,42</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 4,23</t>
+          <t>2,24; 4,04</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,11</t>
+          <t>2,19; 3,14</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,87</t>
+          <t>1,88; 2,76</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,08; 4,14</t>
+          <t>2,07; 4,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,22; 4,05</t>
+          <t>2,28; 4,03</t>
         </is>
       </c>
     </row>
@@ -1556,27 +1556,27 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,47; 3,2</t>
+          <t>2,49; 3,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,5; 3,05</t>
+          <t>2,52; 3,04</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,78</t>
+          <t>2,38; 2,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,69</t>
+          <t>2,56; 3,71</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,02; 2,37</t>
+          <t>2,04; 2,39</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1586,32 +1586,32 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,31; 2,75</t>
+          <t>2,29; 2,77</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,55; 3,12</t>
+          <t>2,56; 3,13</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,36; 2,86</t>
+          <t>2,35; 2,84</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,78</t>
+          <t>2,45; 2,77</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,39; 2,7</t>
+          <t>2,38; 2,7</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,64; 3,27</t>
+          <t>2,63; 3,27</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q24D_2-Clase-trans_orig.xlsx
+++ b/data/trans_orig/Q24D_2-Clase-trans_orig.xlsx
@@ -663,7 +663,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,82</t>
+          <t>2,88</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -683,7 +683,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,51</t>
+          <t>2,54</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>2,68</t>
+          <t>2,73</t>
         </is>
       </c>
     </row>
@@ -716,62 +716,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,83; 2,64</t>
+          <t>1,83; 2,72</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,3; 3,52</t>
+          <t>2,31; 3,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,02; 4,37</t>
+          <t>2,04; 4,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,88</t>
+          <t>2,3; 3,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>1,73; 3,45</t>
+          <t>1,7; 3,32</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,69; 3,89</t>
+          <t>2,65; 3,9</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>1,71; 2,43</t>
+          <t>1,7; 2,48</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>2,11; 3,21</t>
+          <t>2,11; 3,24</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1,89; 2,66</t>
+          <t>1,88; 2,67</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,43</t>
+          <t>2,56; 3,49</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>2,03; 3,36</t>
+          <t>2,04; 3,48</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,27</t>
+          <t>2,35; 3,33</t>
         </is>
       </c>
     </row>
@@ -803,7 +803,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,97</t>
+          <t>2,85</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>2,35</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -843,7 +843,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,65</t>
+          <t>2,59</t>
         </is>
       </c>
     </row>
@@ -856,62 +856,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,58</t>
+          <t>2,23; 4,86</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 3,2</t>
+          <t>2,34; 3,21</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,75; 2,76</t>
+          <t>1,72; 2,8</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2,25; 4,39</t>
+          <t>2,14; 4,12</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 2,39</t>
+          <t>1,66; 2,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,87; 2,62</t>
+          <t>1,86; 2,61</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,67; 2,39</t>
+          <t>1,65; 2,39</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>1,97; 2,84</t>
+          <t>2,02; 2,79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,29</t>
+          <t>2,1; 3,3</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2,22; 2,82</t>
+          <t>2,19; 2,83</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,48</t>
+          <t>1,79; 2,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>2,23; 3,39</t>
+          <t>2,22; 3,24</t>
         </is>
       </c>
     </row>
@@ -943,7 +943,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2,59</t>
+          <t>2,68</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>2,75</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -996,62 +996,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,33</t>
+          <t>2,29; 4,2</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,15</t>
+          <t>2,26; 3,18</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 3,09</t>
+          <t>2,26; 3,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,08; 3,96</t>
+          <t>2,11; 4,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1,35; 2,07</t>
+          <t>1,38; 2,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,94; 2,68</t>
+          <t>1,92; 2,68</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,97</t>
+          <t>1,99; 4,14</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2,34; 4,82</t>
+          <t>2,42; 4,86</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,23; 4,05</t>
+          <t>2,17; 3,82</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,97</t>
+          <t>2,25; 2,97</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2,27; 3,05</t>
+          <t>2,27; 3,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,97</t>
+          <t>2,3; 4,1</t>
         </is>
       </c>
     </row>
@@ -1083,7 +1083,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2,91</t>
+          <t>3,28</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1123,7 +1123,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,19</t>
         </is>
       </c>
     </row>
@@ -1136,27 +1136,27 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,39; 3,62</t>
+          <t>2,42; 3,65</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 3,78</t>
+          <t>2,41; 3,61</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,42; 3,1</t>
+          <t>2,43; 3,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,98</t>
+          <t>2,46; 5,47</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,81; 2,37</t>
+          <t>1,79; 2,35</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1166,32 +1166,32 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,96</t>
+          <t>2,3; 2,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2,65; 3,65</t>
+          <t>2,66; 3,65</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,26; 3,08</t>
+          <t>2,28; 3,07</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,22</t>
+          <t>2,4; 3,18</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>2,44; 2,93</t>
+          <t>2,46; 2,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2,58; 4,05</t>
+          <t>2,7; 4,46</t>
         </is>
       </c>
     </row>
@@ -1223,7 +1223,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3,45</t>
+          <t>3,71</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1243,7 +1243,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>2,67</t>
+          <t>2,73</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1263,7 +1263,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,99</t>
+          <t>3,16</t>
         </is>
       </c>
     </row>
@@ -1276,69 +1276,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 5,23</t>
+          <t>2,16; 5,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,05; 2,93</t>
+          <t>2,11; 2,95</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2,1; 2,89</t>
+          <t>2,1; 2,92</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2,65; 4,78</t>
+          <t>2,72; 5,52</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,59</t>
+          <t>1,87; 2,61</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>2,21; 2,87</t>
+          <t>2,23; 2,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 2,95</t>
+          <t>2,2; 2,95</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>2,18; 3,76</t>
+          <t>2,22; 3,65</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,14; 3,87</t>
+          <t>2,13; 3,92</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 2,77</t>
+          <t>2,26; 2,79</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2,24; 2,82</t>
+          <t>2,24; 2,79</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,51; 3,72</t>
+          <t>2,6; 4,11</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1383,7 +1383,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>2,76</t>
+          <t>2,81</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>2,77</t>
+          <t>2,82</t>
         </is>
       </c>
     </row>
@@ -1416,7 +1416,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,16; 2,96</t>
+          <t>1,16; 2,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1426,7 +1426,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1,67; 3,15</t>
+          <t>1,66; 3,0</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 3,45</t>
+          <t>2,23; 3,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,8; 2,79</t>
+          <t>1,79; 2,74</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,42</t>
+          <t>2,06; 4,76</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,04</t>
+          <t>2,23; 4,26</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2,19; 3,14</t>
+          <t>2,19; 3,18</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,88; 2,76</t>
+          <t>1,9; 2,9</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>2,07; 4,24</t>
+          <t>2,08; 4,32</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>2,28; 4,03</t>
+          <t>2,27; 4,24</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>2,95</t>
+          <t>3,17</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>2,79</t>
+          <t>2,82</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1543,7 +1543,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>2,87</t>
+          <t>2,99</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1556,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,49; 3,25</t>
+          <t>2,48; 3,25</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,04</t>
+          <t>2,5; 3,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,77</t>
+          <t>2,37; 2,77</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,71</t>
+          <t>2,74; 4,03</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>2,04; 2,39</t>
+          <t>2,03; 2,4</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,28; 2,63</t>
+          <t>2,29; 2,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>2,29; 2,77</t>
+          <t>2,32; 2,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>2,56; 3,13</t>
+          <t>2,57; 3,11</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2,35; 2,84</t>
+          <t>2,35; 2,83</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2,45; 2,77</t>
+          <t>2,44; 2,76</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>2,38; 2,7</t>
+          <t>2,4; 2,72</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>2,63; 3,27</t>
+          <t>2,74; 3,45</t>
         </is>
       </c>
     </row>
